--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488166_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488166_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7018</v>
+        <v>3.6695</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.9751</v>
+        <v>-0.9089</v>
       </c>
       <c r="F2" t="n">
-        <v>4.677</v>
+        <v>4.5785</v>
       </c>
       <c r="G2" t="n">
         <v>2.4722</v>
@@ -610,13 +610,13 @@
         <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5996</v>
+        <v>0.5674</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4539</v>
+        <v>-0.3876</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0535</v>
+        <v>0.955</v>
       </c>
       <c r="V2" t="n">
         <v>0.63</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0916</v>
+        <v>2.8366</v>
       </c>
       <c r="E3" t="n">
-        <v>2.862</v>
+        <v>3.1241</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2296</v>
+        <v>-0.2874</v>
       </c>
       <c r="G3" t="n">
         <v>2.0647</v>
@@ -688,13 +688,13 @@
         <v>1.297</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6737</v>
+        <v>0.4188</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3743</v>
+        <v>-0.1122</v>
       </c>
       <c r="U3" t="n">
-        <v>1.048</v>
+        <v>0.531</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9439</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2026</v>
+        <v>1.3251</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.9977</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3028</v>
+        <v>0.3275</v>
       </c>
       <c r="G4" t="n">
         <v>1.1862</v>
@@ -766,13 +766,13 @@
         <v>0.1853</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1689</v>
+        <v>-0.0463</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1094</v>
+        <v>-0.0115</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0594</v>
+        <v>-0.0348</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. TORRES VELEZ</t>
+          <t>A. RODRIGUEZ LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5121</v>
+        <v>1.2764</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6213</v>
+        <v>-1.4973</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1335</v>
+        <v>2.7738</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1469</v>
+        <v>-0.187</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0482</v>
+        <v>-1.2686</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.195</v>
+        <v>1.0815</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4095</v>
+        <v>-1.2959</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9273</v>
+        <v>-1.3789</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5178</v>
+        <v>0.0829</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5564</v>
+        <v>1.1089</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8791</v>
+        <v>0.1103</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3227</v>
+        <v>0.9986</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1117</v>
+        <v>2.0382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>2.0382</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1383</v>
+        <v>0.0547</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1044</v>
+        <v>-0.2014</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0338</v>
+        <v>0.2561</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3144</v>
+        <v>-0.6294</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3144</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LOPEZ</t>
+          <t>J. TORRES VELEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4251</v>
+        <v>0.702</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0532</v>
+        <v>-0.6531</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4783</v>
+        <v>1.3551</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.187</v>
+        <v>-0.1469</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2686</v>
+        <v>0.0482</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0815</v>
+        <v>-0.195</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2959</v>
+        <v>0.4095</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.3789</v>
+        <v>0.9273</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0829</v>
+        <v>-0.5178</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1089</v>
+        <v>-0.5564</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1103</v>
+        <v>-0.8791</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9986</v>
+        <v>0.3227</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0382</v>
+        <v>1.1117</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
         <v>2.0382</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7966</v>
+        <v>0.0516</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7573</v>
+        <v>-0.1361</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0393</v>
+        <v>0.1878</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6294</v>
+        <v>-0.3144</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6294</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. QUESADA PONS</t>
+          <t>M. ORTEGA CARO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3603</v>
+        <v>-0.428</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4851</v>
+        <v>-0.663</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1248</v>
+        <v>0.235</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2235</v>
+        <v>1.0529</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4387</v>
+        <v>-0.1543</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2152</v>
+        <v>1.2072</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1503</v>
+        <v>1.7485</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1503</v>
+        <v>0.4724</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.2762</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3738</v>
+        <v>-0.6957</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.589</v>
+        <v>-0.6267</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2152</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1853</v>
+        <v>-1.297</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0485</v>
+        <v>-0.1844</v>
       </c>
       <c r="T7" t="n">
-        <v>0.291</v>
+        <v>-0.5586</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2425</v>
+        <v>0.3743</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ORTEGA CARO</t>
+          <t>P. QUESADA PONS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8761</v>
+        <v>-0.4763</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8156</v>
+        <v>-0.7242</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0604</v>
+        <v>0.2479</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0529</v>
+        <v>-0.2235</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1543</v>
+        <v>-0.4387</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2072</v>
+        <v>0.2152</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7485</v>
+        <v>0.1503</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4724</v>
+        <v>0.1503</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2762</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6957</v>
+        <v>-0.3738</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6267</v>
+        <v>-0.589</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.2152</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.297</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6325</v>
+        <v>-0.0675</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7113</v>
+        <v>0.0519</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0788</v>
+        <v>-0.1194</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. RUEDA MURIEL</t>
+          <t>T. LUCERO BARBEITO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3192</v>
+        <v>-0.5115</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6923</v>
+        <v>-1.603</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3731</v>
+        <v>1.0915</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1065</v>
+        <v>-1.5083</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4492</v>
+        <v>-2.1164</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6574</v>
+        <v>0.6081</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1998</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5884</v>
+        <v>-0.7991</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.0012</v>
       </c>
       <c r="M9" t="n">
-        <v>0.09329999999999999</v>
+        <v>-0.7104</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1393</v>
+        <v>-1.3173</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.046</v>
+        <v>0.6069</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1853</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1853</v>
+        <v>1.6676</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3979</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4924</v>
+        <v>-0.2111</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0945</v>
+        <v>0.1343</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MORALES ZARCO</t>
+          <t>M. RUEDA MURIEL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3569</v>
+        <v>-1.0434</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3851</v>
+        <v>-1.5396</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0282</v>
+        <v>0.4962</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4728</v>
+        <v>-1.1065</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8245</v>
+        <v>-0.4492</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6483</v>
+        <v>-0.6574</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2334</v>
+        <v>-1.1998</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8448</v>
+        <v>-0.5884</v>
       </c>
       <c r="L10" t="n">
         <v>-0.6114000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2395</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0203</v>
+        <v>0.1393</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2597</v>
+        <v>-0.046</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.1853</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.297</v>
+        <v>0.1853</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4493</v>
+        <v>-0.1222</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7549</v>
+        <v>-0.3398</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6944</v>
+        <v>0.2176</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.7232</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-2.5205</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.2027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. LUCERO BARBEITO</t>
+          <t>A. TEJADA CAMACHO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3634</v>
+        <v>-2.8947</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0609</v>
+        <v>-5.0832</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6975</v>
+        <v>2.1885</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5083</v>
+        <v>1.4084</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1164</v>
+        <v>2.6357</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6081</v>
+        <v>-1.2273</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7979000000000001</v>
+        <v>1.3203</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7991</v>
+        <v>2.5631</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0012</v>
+        <v>-1.2429</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7104</v>
+        <v>0.0882</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3173</v>
+        <v>0.0726</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6069</v>
+        <v>0.0156</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1853</v>
+        <v>-4.4469</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8529</v>
+        <v>-5.5586</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6676</v>
+        <v>1.1117</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9287</v>
+        <v>0.4598</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.669</v>
+        <v>-0.5288</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2597</v>
+        <v>0.9886</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2589</v>
+        <v>-0.3161</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2589</v>
+        <v>-0.3161</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. TEJADA CAMACHO</t>
+          <t>J. MORALES ZARCO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2421</v>
+        <v>-2.9463</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.6276</v>
+        <v>-4.3097</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3855</v>
+        <v>1.3634</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4084</v>
+        <v>1.4728</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6357</v>
+        <v>0.8245</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2273</v>
+        <v>0.6483</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3203</v>
+        <v>0.2334</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5631</v>
+        <v>0.8448</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2429</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0882</v>
+        <v>1.2395</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0726</v>
+        <v>-0.0203</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0156</v>
+        <v>1.2597</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.4469</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.5586</v>
+        <v>-1.8529</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1117</v>
+        <v>1.297</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1124</v>
+        <v>0.8599</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0732</v>
+        <v>-0.1697</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1856</v>
+        <v>1.0296</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3161</v>
+        <v>-4.7232</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3161</v>
+        <v>-2.5205</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4152000000000013</v>
+        <v>1.509399999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.9545</v>
+        <v>-12.8602</v>
       </c>
       <c r="F13" t="n">
-        <v>14.3699</v>
+        <v>14.37</v>
       </c>
       <c r="G13" t="n">
         <v>6.485</v>
@@ -1447,19 +1447,19 @@
         <v>6.2235</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.07810000000000006</v>
+        <v>-0.07810000000000017</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3396999999999999</v>
+        <v>0.3397000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.308400000000001</v>
+        <v>-4.3084</v>
       </c>
       <c r="O13" t="n">
-        <v>4.647999999999999</v>
+        <v>4.648000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.8529</v>
+        <v>-1.852900000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-14.823</v>
@@ -1468,13 +1468,13 @@
         <v>12.9702</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8205999999999998</v>
+        <v>1.915</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.6993</v>
+        <v>-2.6049</v>
       </c>
       <c r="U13" t="n">
-        <v>4.520099999999999</v>
+        <v>4.5201</v>
       </c>
       <c r="V13" t="n">
         <v>-5.0376</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0272</v>
+        <v>3.2281</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6659</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6931</v>
+        <v>3.3064</v>
       </c>
       <c r="G14" t="n">
         <v>2.3212</v>
@@ -1546,13 +1546,13 @@
         <v>2.4087</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9976</v>
+        <v>0.2033</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5444</v>
+        <v>-0.9569</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5469000000000001</v>
+        <v>1.1602</v>
       </c>
       <c r="V14" t="n">
         <v>1.2594</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7038</v>
+        <v>1.7295</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.4911</v>
+        <v>0.3183</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1949</v>
+        <v>1.4112</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.1898</v>
+        <v>1.5187</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8566</v>
+        <v>-1.0126</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3332</v>
+        <v>2.5314</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.8017</v>
+        <v>1.4779</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5374</v>
+        <v>-0.5542</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.2643</v>
+        <v>2.0321</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3881</v>
+        <v>0.0409</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3191</v>
+        <v>-0.4584</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.4993</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3706</v>
+        <v>0.3706</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0382</v>
+        <v>-0.9264</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6676</v>
+        <v>1.297</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3759</v>
+        <v>-0.1598</v>
       </c>
       <c r="T15" t="n">
-        <v>0.776</v>
+        <v>-0.2331</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5999</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8883</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5727</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.615</v>
+        <v>1.6342</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5141</v>
+        <v>-1.6052</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1009</v>
+        <v>3.2394</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5187</v>
+        <v>-0.046</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0126</v>
+        <v>0.2611</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5314</v>
+        <v>-0.3071</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4779</v>
+        <v>0.1885</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5542</v>
+        <v>0.8414</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0321</v>
+        <v>-0.6529</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0409</v>
+        <v>-0.2345</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4584</v>
+        <v>-0.5803</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4993</v>
+        <v>0.3457</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3706</v>
+        <v>1.1117</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9264</v>
+        <v>-1.1117</v>
       </c>
       <c r="R16" t="n">
-        <v>1.297</v>
+        <v>2.2234</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2743</v>
+        <v>-0.0609</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0373</v>
+        <v>-0.6814</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.237</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4342</v>
+        <v>1.3346</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9599</v>
+        <v>-0.7641</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3941</v>
+        <v>2.0987</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2836</v>
@@ -1780,13 +1780,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1985</v>
+        <v>0.0989</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4924</v>
+        <v>-0.2966</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6909</v>
+        <v>0.3954</v>
       </c>
       <c r="V17" t="n">
         <v>1.8899</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. OSES BERNALDEZ</t>
+          <t>P. OSÉS BERNALDÉZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1933</v>
+        <v>0.3221</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9969</v>
+        <v>0.3221</v>
       </c>
       <c r="F18" t="n">
-        <v>3.1901</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.046</v>
+        <v>0.3221</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2611</v>
+        <v>0.3221</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3071</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1885</v>
+        <v>0.3221</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8414</v>
+        <v>0.3221</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6529</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2345</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5803</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3457</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2234</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5019</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0732</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5713</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. OSÉS BERNALDÉZ</t>
+          <t>J. NIELSEN HIDALGO MARTÍN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTÍN</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3221</v>
+        <v>0.2155</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3221</v>
+        <v>-2.5683</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2.7838</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3221</v>
+        <v>-2.1898</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3221</v>
+        <v>-0.8566</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-1.3332</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3221</v>
+        <v>-1.8017</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3221</v>
+        <v>-0.5374</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.2643</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-0.3881</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.3191</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.3012</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.1888</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.8883</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.5727</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5208</v>
+        <v>-0.6176</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2466</v>
+        <v>-0.5403</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2742</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-1.367</v>
@@ -2092,13 +2092,13 @@
         <v>1.1117</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.58</v>
+        <v>-0.6768</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0584</v>
+        <v>-0.3522</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5215</v>
+        <v>-0.3246</v>
       </c>
       <c r="V21" t="n">
         <v>0.3144</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6189</v>
+        <v>-0.6836</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6662</v>
+        <v>-0.96</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0473</v>
+        <v>0.2763</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5774</v>
@@ -2170,13 +2170,13 @@
         <v>0.7411</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1532</v>
+        <v>-0.2179</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1057</v>
+        <v>-0.1881</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2589</v>
+        <v>-0.0299</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6294</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. MENDEZ CARRION</t>
+          <t>I. VAZQUEZ FLORES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7096</v>
+        <v>-1.3279</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5758</v>
+        <v>-1.2921</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8662</v>
+        <v>-0.0358</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.4365</v>
+        <v>-0.4135</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6085</v>
+        <v>1.1287</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.828</v>
+        <v>-1.5422</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.8447</v>
+        <v>0.2822</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.654</v>
+        <v>1.4943</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1907</v>
+        <v>-1.2121</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5918</v>
+        <v>-0.6957</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9545</v>
+        <v>-0.3656</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6373</v>
+        <v>-0.3301</v>
       </c>
       <c r="P23" t="n">
-        <v>1.297</v>
+        <v>0.1853</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.1117</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4087</v>
+        <v>1.297</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4855</v>
+        <v>0.1592</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5633</v>
+        <v>-0.4626</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0488</v>
+        <v>0.6218</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9444</v>
+        <v>-1.2589</v>
       </c>
       <c r="W23" t="n">
-        <v>0.9439</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0005</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ FLORES</t>
+          <t>A. MENDEZ CARRION</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3329</v>
+        <v>-1.5223</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6838</v>
+        <v>-3.5758</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6491</v>
+        <v>2.0535</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4135</v>
+        <v>-4.4365</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1287</v>
+        <v>-2.6085</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.5422</v>
+        <v>-1.828</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2822</v>
+        <v>-2.8447</v>
       </c>
       <c r="K24" t="n">
-        <v>1.4943</v>
+        <v>-1.654</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2121</v>
+        <v>-1.1907</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6957</v>
+        <v>-1.5918</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3656</v>
+        <v>-0.9545</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3301</v>
+        <v>-0.6373</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1853</v>
+        <v>1.297</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.1117</v>
       </c>
       <c r="R24" t="n">
-        <v>1.297</v>
+        <v>2.4087</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8458</v>
+        <v>0.6728</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.5633</v>
       </c>
       <c r="U24" t="n">
-        <v>0.008399999999999999</v>
+        <v>1.236</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2589</v>
+        <v>0.9444</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.9439</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2589</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8506</v>
+        <v>-3.0912</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2419</v>
+        <v>-3.9481</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3913</v>
+        <v>0.8569</v>
       </c>
       <c r="G25" t="n">
         <v>-1.6553</v>
@@ -2404,13 +2404,13 @@
         <v>1.1117</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5278</v>
+        <v>0.2316</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7784</v>
+        <v>-0.4846</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2507</v>
+        <v>0.7163</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4151000000000002</v>
+        <v>1.5435</v>
       </c>
       <c r="E26" t="n">
-        <v>-14.3698</v>
+        <v>-14.3697</v>
       </c>
       <c r="F26" t="n">
-        <v>13.9546</v>
+        <v>15.9131</v>
       </c>
       <c r="G26" t="n">
         <v>-6.484999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.9149</v>
+        <v>-1.914899999999999</v>
       </c>
       <c r="I26" t="n">
         <v>-4.5698</v>
@@ -2461,16 +2461,16 @@
         <v>4.3085</v>
       </c>
       <c r="L26" t="n">
-        <v>-4.648000000000001</v>
+        <v>-4.648</v>
       </c>
       <c r="M26" t="n">
         <v>-6.1454</v>
       </c>
       <c r="N26" t="n">
-        <v>-6.223300000000001</v>
+        <v>-6.2233</v>
       </c>
       <c r="O26" t="n">
-        <v>0.07800000000000007</v>
+        <v>0.07800000000000001</v>
       </c>
       <c r="P26" t="n">
         <v>1.8527</v>
@@ -2482,19 +2482,19 @@
         <v>14.8228</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8206999999999999</v>
+        <v>1.138</v>
       </c>
       <c r="T26" t="n">
         <v>-4.52</v>
       </c>
       <c r="U26" t="n">
-        <v>3.6995</v>
+        <v>5.6579</v>
       </c>
       <c r="V26" t="n">
         <v>5.037500000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>3.459899999999999</v>
+        <v>3.4599</v>
       </c>
       <c r="X26" t="n">
         <v>1.5776</v>
